--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-transport-usager.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-transport-usager.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T14:23:39+00:00</t>
+    <t>2026-01-28T15:00:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-transport-usager.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-transport-usager.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T15:00:38+00:00</t>
+    <t>2026-01-28T15:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1518,7 +1518,7 @@
     <t>Inputs are named to enable task automation to bind data and pass it from one task to the next.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/input-tddui-task-transport-valueset|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/input-tddui-task-transport|2.2.0-ballot</t>
   </si>
   <si>
     <t>Task.input.value[x]</t>
@@ -1557,7 +1557,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
     &lt;code value="typeMotorisation"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1592,7 +1592,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
     &lt;code value="adresseDepart"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1628,7 +1628,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
     &lt;code value="adresseDestination"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1660,7 +1660,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
     &lt;code value="budgetPrevisionnel"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1696,7 +1696,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
     &lt;code value="budgetReel"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1728,7 +1728,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
     &lt;code value="distance"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1764,7 +1764,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
     &lt;code value="dureeTheorique"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1800,7 +1800,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
     &lt;code value="accompagnement"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1836,7 +1836,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
     &lt;code value="asepsie"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1868,7 +1868,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
     &lt;code value="natureTransport"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-transport-usager.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-transport-usager.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T15:51:30+00:00</t>
+    <t>2026-02-02T09:49:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1518,7 +1518,7 @@
     <t>Inputs are named to enable task automation to bind data and pass it from one task to the next.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/input-tddui-task-transport|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-task-input-transport|2.2.0-ballot</t>
   </si>
   <si>
     <t>Task.input.value[x]</t>
@@ -1557,7 +1557,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="typeMotorisation"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1592,7 +1592,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="adresseDepart"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1628,7 +1628,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="adresseDestination"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1660,7 +1660,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="budgetPrevisionnel"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1696,7 +1696,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="budgetReel"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1728,7 +1728,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="distance"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1764,7 +1764,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="dureeTheorique"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1800,7 +1800,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="accompagnement"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1836,7 +1836,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="asepsie"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1868,7 +1868,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="natureTransport"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-transport-usager.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-transport-usager.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:49:54+00:00</t>
+    <t>2026-02-02T14:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-transport-usager.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-transport-usager.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T14:44:55+00:00</t>
+    <t>2026-02-04T16:15:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-transport-usager.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-task-transport-usager.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T16:15:13+00:00</t>
+    <t>2026-02-05T08:25:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
